--- a/artfynd/A 16924-2026 artfynd.xlsx
+++ b/artfynd/A 16924-2026 artfynd.xlsx
@@ -2232,7 +2232,7 @@
         <v>136125557</v>
       </c>
       <c r="B15" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
